--- a/product_upload/packages/3/file.xlsx
+++ b/product_upload/packages/3/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR101"/>
+  <dimension ref="A1:AS101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,7 +590,7 @@
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
@@ -639,6 +639,11 @@
         </is>
       </c>
       <c r="AR1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -667,7 +672,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -818,6 +823,11 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
+          <t>QUINOX 250 MG F- C TAB</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>SKU-67EF75307570</t>
         </is>
       </c>
@@ -845,7 +855,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -996,6 +1006,11 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
+          <t>RAZON 40 MG E.C TAB</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
           <t>SKU-A0ABE4FD5360</t>
         </is>
       </c>
@@ -1023,7 +1038,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1178,6 +1193,11 @@
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr">
         <is>
+          <t>RAZON 20 MG E.C. TABLET</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
           <t>SKU-206883CDE53F</t>
         </is>
       </c>
@@ -1205,7 +1225,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1364,6 +1384,11 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
+          <t>RAPIDUS 50 MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
           <t>SKU-7CBCA1059D04</t>
         </is>
       </c>
@@ -1391,7 +1416,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1542,6 +1567,11 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
+          <t>RAPIDUS 25MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
           <t>SKU-3677E0BB136F</t>
         </is>
       </c>
@@ -1569,7 +1599,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1720,6 +1750,11 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
+          <t>QUESTRAN POWDER</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
           <t>SKU-4FED9FFDFC75</t>
         </is>
       </c>
@@ -1747,7 +1782,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1906,6 +1941,11 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
+          <t>PYRAZINAMIDE ANTIBIOTICE</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
           <t>SKU-2918BDC3DF4A</t>
         </is>
       </c>
@@ -1933,7 +1973,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2088,6 +2128,11 @@
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr">
         <is>
+          <t>PROTON 40MG E.C TAB</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
           <t>SKU-2810B2641909</t>
         </is>
       </c>
@@ -2115,7 +2160,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2262,6 +2307,11 @@
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr">
         <is>
+          <t>PROTON 40MG E.C TAB</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
           <t>SKU-82EB14F46952</t>
         </is>
       </c>
@@ -2289,7 +2339,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2440,6 +2490,11 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
+          <t>PROTON 20MG E.C TABLET</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
           <t>SKU-851D06D44DBF</t>
         </is>
       </c>
@@ -2467,7 +2522,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2622,6 +2677,11 @@
       <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="inlineStr">
         <is>
+          <t>PROTON 20MG E.C TABLET</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
           <t>SKU-5034CCBDC1CB</t>
         </is>
       </c>
@@ -2649,7 +2709,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2804,6 +2864,11 @@
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr">
         <is>
+          <t>PROTOGYN</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
           <t>SKU-7018CB22073E</t>
         </is>
       </c>
@@ -2831,7 +2896,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2982,6 +3047,11 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
+          <t>PROTHIADEN TAB 75MG</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
           <t>SKU-2F9A971C0D53</t>
         </is>
       </c>
@@ -3009,7 +3079,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3156,6 +3226,11 @@
       <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="inlineStr">
         <is>
+          <t>PROTHIADEN 25MG CAPS</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
           <t>SKU-A187379F773B</t>
         </is>
       </c>
@@ -3183,7 +3258,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3340,6 +3415,11 @@
       <c r="AQ16" t="inlineStr"/>
       <c r="AR16" t="inlineStr">
         <is>
+          <t>PULMICORT 0.5MG-ML (S.DOSE FOR NUB) SUSP</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
           <t>SKU-76265B28C73C</t>
         </is>
       </c>
@@ -3367,7 +3447,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3520,6 +3600,11 @@
       <c r="AQ17" t="inlineStr"/>
       <c r="AR17" t="inlineStr">
         <is>
+          <t>PULMICORT TURBUHALER 100MCG-DOSE</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
           <t>SKU-44BD0A284697</t>
         </is>
       </c>
@@ -3547,7 +3632,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3704,6 +3789,11 @@
       <c r="AQ18" t="inlineStr"/>
       <c r="AR18" t="inlineStr">
         <is>
+          <t>PULMICORT TURBUHALER 200MCG-DOSE</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
           <t>SKU-E8B322C699FC</t>
         </is>
       </c>
@@ -3731,7 +3821,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3888,6 +3978,11 @@
       <c r="AQ19" t="inlineStr"/>
       <c r="AR19" t="inlineStr">
         <is>
+          <t>PYRALVEX</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
           <t>SKU-6FCC0B91F802</t>
         </is>
       </c>
@@ -3915,7 +4010,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4078,6 +4173,11 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
+          <t>PUREGON 600 I.U CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
           <t>SKU-7F21384EF0B7</t>
         </is>
       </c>
@@ -4105,7 +4205,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4250,6 +4350,11 @@
       <c r="AQ21" t="inlineStr"/>
       <c r="AR21" t="inlineStr">
         <is>
+          <t>PULMICORT0.25MG-ML SINGLE DOSE PLASTIC U</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
           <t>SKU-0F3D9E18EF37</t>
         </is>
       </c>
@@ -4277,7 +4382,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4440,6 +4545,11 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
+          <t>PUREGON 300I.U CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
           <t>SKU-04E75AE92823</t>
         </is>
       </c>
@@ -4467,7 +4577,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4618,6 +4728,11 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
+          <t>PREGADEX 300 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
           <t>SKU-8A4A401B797D</t>
         </is>
       </c>
@@ -4645,7 +4760,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4804,6 +4919,11 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
+          <t>PREGADEX 150 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
           <t>SKU-B9AF556AC7B8</t>
         </is>
       </c>
@@ -4831,7 +4951,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4990,6 +5110,11 @@
       <c r="AQ25" t="inlineStr"/>
       <c r="AR25" t="inlineStr">
         <is>
+          <t>PERIACTIN 4MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
           <t>SKU-DA5DF163D0A7</t>
         </is>
       </c>
@@ -5017,7 +5142,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5174,6 +5299,11 @@
       <c r="AQ26" t="inlineStr"/>
       <c r="AR26" t="inlineStr">
         <is>
+          <t>PERGOVERIS 150/75 IU vial</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
           <t>SKU-9CDAC50914AD</t>
         </is>
       </c>
@@ -5201,7 +5331,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5360,6 +5490,11 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
+          <t>PEPTAZOLE 30MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
           <t>SKU-20479AF63471</t>
         </is>
       </c>
@@ -5387,7 +5522,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5546,6 +5681,11 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
+          <t>PEPTAZOLE 30MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
           <t>SKU-F86D12E8A989</t>
         </is>
       </c>
@@ -5573,7 +5713,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5728,6 +5868,11 @@
       <c r="AQ29" t="inlineStr"/>
       <c r="AR29" t="inlineStr">
         <is>
+          <t>PEPTAZOLE 15MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
           <t>SKU-0EBB13365B92</t>
         </is>
       </c>
@@ -5755,7 +5900,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5914,6 +6059,11 @@
       </c>
       <c r="AR30" t="inlineStr">
         <is>
+          <t>PEPTAZOLE 15MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
           <t>SKU-BFD291044260</t>
         </is>
       </c>
@@ -5941,7 +6091,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6096,6 +6246,11 @@
       <c r="AQ31" t="inlineStr"/>
       <c r="AR31" t="inlineStr">
         <is>
+          <t>PENTOLATE 1% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
           <t>SKU-0E4AAAE834C9</t>
         </is>
       </c>
@@ -6123,7 +6278,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6282,6 +6437,11 @@
       </c>
       <c r="AR32" t="inlineStr">
         <is>
+          <t>PECTAL 100MG\5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
           <t>SKU-C11C59E74F23</t>
         </is>
       </c>
@@ -6309,7 +6469,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6460,6 +6620,11 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
+          <t>PAXITAB 40MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
           <t>SKU-09BCDF79C55C</t>
         </is>
       </c>
@@ -6487,7 +6652,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6638,6 +6803,11 @@
       <c r="AQ34" t="inlineStr"/>
       <c r="AR34" t="inlineStr">
         <is>
+          <t>PAXITAB 20MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
           <t>SKU-EB0CBE3E6907</t>
         </is>
       </c>
@@ -6665,7 +6835,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6816,6 +6986,11 @@
       <c r="AQ35" t="inlineStr"/>
       <c r="AR35" t="inlineStr">
         <is>
+          <t>PAROXAT 30MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
           <t>SKU-123C03CBC313</t>
         </is>
       </c>
@@ -6843,7 +7018,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6998,6 +7173,11 @@
       <c r="AQ36" t="inlineStr"/>
       <c r="AR36" t="inlineStr">
         <is>
+          <t>PAROXAT 20 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
           <t>SKU-F57D17D074FF</t>
         </is>
       </c>
@@ -7025,7 +7205,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7180,6 +7360,11 @@
       <c r="AQ37" t="inlineStr"/>
       <c r="AR37" t="inlineStr">
         <is>
+          <t>PAROXAT 10 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
           <t>SKU-5835F01AE4F1</t>
         </is>
       </c>
@@ -7207,7 +7392,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7362,6 +7547,11 @@
       <c r="AQ38" t="inlineStr"/>
       <c r="AR38" t="inlineStr">
         <is>
+          <t>PARIET 20MG E.C TAB</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
           <t>SKU-2C98CDD58340</t>
         </is>
       </c>
@@ -7389,7 +7579,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7548,6 +7738,11 @@
       <c r="AQ39" t="inlineStr"/>
       <c r="AR39" t="inlineStr">
         <is>
+          <t>PEDIAMOL 100MG-ML ORAL DROPS</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
           <t>SKU-F72563E9044B</t>
         </is>
       </c>
@@ -7575,7 +7770,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7734,6 +7929,11 @@
       </c>
       <c r="AR40" t="inlineStr">
         <is>
+          <t>PENTASA 500 MG SLOW RELEASE TABLET</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
           <t>SKU-31ED96B887E8</t>
         </is>
       </c>
@@ -7761,7 +7961,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7920,6 +8120,11 @@
       </c>
       <c r="AR41" t="inlineStr">
         <is>
+          <t>PENTASA 1GM SUPP.</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
           <t>SKU-4E23FABDA3F9</t>
         </is>
       </c>
@@ -7947,7 +8152,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8094,6 +8299,11 @@
       <c r="AQ42" t="inlineStr"/>
       <c r="AR42" t="inlineStr">
         <is>
+          <t>PENTASA 1GM PROLONGED RELEASE GRANULES</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
           <t>SKU-F34D7236F90B</t>
         </is>
       </c>
@@ -8121,7 +8331,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8264,6 +8474,11 @@
       <c r="AQ43" t="inlineStr"/>
       <c r="AR43" t="inlineStr">
         <is>
+          <t>PENTASA 1% ENEMA</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
           <t>SKU-5FD886503927</t>
         </is>
       </c>
@@ -8291,7 +8506,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8446,6 +8661,11 @@
       <c r="AQ44" t="inlineStr"/>
       <c r="AR44" t="inlineStr">
         <is>
+          <t>PENTASA 1 G CONTROLLED RELEASE TABLET</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
           <t>SKU-5A3CF05314E9</t>
         </is>
       </c>
@@ -8473,7 +8693,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8632,6 +8852,11 @@
       <c r="AQ45" t="inlineStr"/>
       <c r="AR45" t="inlineStr">
         <is>
+          <t>PONSTAN FORTE 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
           <t>SKU-5AB6A709DBAE</t>
         </is>
       </c>
@@ -8659,7 +8884,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8810,6 +9035,11 @@
       </c>
       <c r="AR46" t="inlineStr">
         <is>
+          <t>POLY-VI-SOL ORAL DROPS</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
           <t>SKU-3AB058FFAE01</t>
         </is>
       </c>
@@ -8837,7 +9067,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -8984,6 +9214,11 @@
       <c r="AQ47" t="inlineStr"/>
       <c r="AR47" t="inlineStr">
         <is>
+          <t>POLYTAR 1% LIQUID SHAMPOO</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
           <t>SKU-A573A046117E</t>
         </is>
       </c>
@@ -9011,7 +9246,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9170,6 +9405,11 @@
       </c>
       <c r="AR48" t="inlineStr">
         <is>
+          <t>PLAVIX 75 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
           <t>SKU-E2E15AD31DD0</t>
         </is>
       </c>
@@ -9197,7 +9437,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9348,6 +9588,11 @@
       <c r="AQ49" t="inlineStr"/>
       <c r="AR49" t="inlineStr">
         <is>
+          <t>POTASSIUM ACETATE INJ F.T.V. 40MEQ</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
           <t>SKU-C435DD3C9A1A</t>
         </is>
       </c>
@@ -9375,7 +9620,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9522,6 +9767,11 @@
       <c r="AQ50" t="inlineStr"/>
       <c r="AR50" t="inlineStr">
         <is>
+          <t>POTASSIUM CHLORIDE 7.5% AMP</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
           <t>SKU-570EBD26BA64</t>
         </is>
       </c>
@@ -9549,7 +9799,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9700,6 +9950,11 @@
       </c>
       <c r="AR51" t="inlineStr">
         <is>
+          <t>PREDO 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
           <t>SKU-51897F6F93CC</t>
         </is>
       </c>
@@ -9727,7 +9982,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9878,6 +10133,11 @@
       <c r="AQ52" t="inlineStr"/>
       <c r="AR52" t="inlineStr">
         <is>
+          <t>PREDO 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
           <t>SKU-41079CCB53D7</t>
         </is>
       </c>
@@ -9905,7 +10165,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10056,6 +10316,11 @@
       <c r="AQ53" t="inlineStr"/>
       <c r="AR53" t="inlineStr">
         <is>
+          <t>PREDO 25MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
           <t>SKU-5D3DF7163FD7</t>
         </is>
       </c>
@@ -10083,7 +10348,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10238,6 +10503,11 @@
       <c r="AQ54" t="inlineStr"/>
       <c r="AR54" t="inlineStr">
         <is>
+          <t>PREDO 15MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
           <t>SKU-F01D0AED65FD</t>
         </is>
       </c>
@@ -10265,7 +10535,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10416,6 +10686,11 @@
       <c r="AQ55" t="inlineStr"/>
       <c r="AR55" t="inlineStr">
         <is>
+          <t>PREDNISOLONE</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
           <t>SKU-9213B76D892E</t>
         </is>
       </c>
@@ -10443,7 +10718,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10598,6 +10873,11 @@
       <c r="AQ56" t="inlineStr"/>
       <c r="AR56" t="inlineStr">
         <is>
+          <t>PRED FORTE OPTH. SUSP</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
           <t>SKU-80948DE99BEC</t>
         </is>
       </c>
@@ -10625,7 +10905,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10786,6 +11066,11 @@
       <c r="AQ57" t="inlineStr"/>
       <c r="AR57" t="inlineStr">
         <is>
+          <t>PRADAXA 75MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
           <t>SKU-2204C34FB27D</t>
         </is>
       </c>
@@ -10813,7 +11098,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -10978,6 +11263,11 @@
       </c>
       <c r="AR58" t="inlineStr">
         <is>
+          <t>PRADAXA 150MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
           <t>SKU-E1F0886337AD</t>
         </is>
       </c>
@@ -11005,7 +11295,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11162,6 +11452,11 @@
       </c>
       <c r="AR59" t="inlineStr">
         <is>
+          <t>PRADAXA 110MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
           <t>SKU-4BD3DE8E243E</t>
         </is>
       </c>
@@ -11189,7 +11484,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11354,6 +11649,11 @@
       </c>
       <c r="AR60" t="inlineStr">
         <is>
+          <t>PRADAXA 110MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
           <t>SKU-BF654D2FE7D9</t>
         </is>
       </c>
@@ -11381,7 +11681,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11528,6 +11828,11 @@
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="inlineStr">
         <is>
+          <t>POTASSIUM CHLORIDE 7.5% AMP</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
           <t>SKU-B211A71DE380</t>
         </is>
       </c>
@@ -11555,7 +11860,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11706,6 +12011,11 @@
       </c>
       <c r="AR62" t="inlineStr">
         <is>
+          <t>POTASSIUM CHLORIDE 7.5% AMP</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
           <t>SKU-DB3BA9F17F69</t>
         </is>
       </c>
@@ -11733,7 +12043,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -11886,6 +12196,11 @@
       <c r="AQ63" t="inlineStr"/>
       <c r="AR63" t="inlineStr">
         <is>
+          <t>PRADAXA 75MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
           <t>SKU-F5DEE48A7679</t>
         </is>
       </c>
@@ -11913,7 +12228,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12064,6 +12379,11 @@
       <c r="AQ64" t="inlineStr"/>
       <c r="AR64" t="inlineStr">
         <is>
+          <t>PHENICOL 1% OPTHALMIC OINTMENT</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
           <t>SKU-6F210825541A</t>
         </is>
       </c>
@@ -12091,7 +12411,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12234,6 +12554,11 @@
       <c r="AQ65" t="inlineStr"/>
       <c r="AR65" t="inlineStr">
         <is>
+          <t>PHAZYME TAB 60MG</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
           <t>SKU-BFA856BA4A1D</t>
         </is>
       </c>
@@ -12261,7 +12586,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12412,6 +12737,11 @@
       </c>
       <c r="AR66" t="inlineStr">
         <is>
+          <t>PHAZYME TAB 60MG</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
           <t>SKU-9EAA99E3C613</t>
         </is>
       </c>
@@ -12439,7 +12769,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12598,6 +12928,11 @@
       </c>
       <c r="AR67" t="inlineStr">
         <is>
+          <t>NO-URIC 100 mg tablet</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
           <t>SKU-C5DAAB923846</t>
         </is>
       </c>
@@ -12625,7 +12960,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12772,6 +13107,11 @@
       <c r="AQ68" t="inlineStr"/>
       <c r="AR68" t="inlineStr">
         <is>
+          <t>PHILAQUIN FORTE 4% CREAM</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
           <t>SKU-0B67BF29C833</t>
         </is>
       </c>
@@ -12799,7 +13139,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -12958,6 +13298,11 @@
       </c>
       <c r="AR69" t="inlineStr">
         <is>
+          <t>PK-MERZ</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
           <t>SKU-1096B82540A7</t>
         </is>
       </c>
@@ -12985,7 +13330,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13134,6 +13479,11 @@
       <c r="AQ70" t="inlineStr"/>
       <c r="AR70" t="inlineStr">
         <is>
+          <t>PIGMANORM</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
           <t>SKU-614048E08F8E</t>
         </is>
       </c>
@@ -13161,7 +13511,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13318,6 +13668,11 @@
       <c r="AQ71" t="inlineStr"/>
       <c r="AR71" t="inlineStr">
         <is>
+          <t>PICOPREP POWDER FOR ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
           <t>SKU-0D61344E5429</t>
         </is>
       </c>
@@ -13345,7 +13700,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13504,6 +13859,11 @@
       </c>
       <c r="AR72" t="inlineStr">
         <is>
+          <t>PICO 7.5MG-ML ORAL DROPS</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
           <t>SKU-29D7548CBBF3</t>
         </is>
       </c>
@@ -13531,7 +13891,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13688,6 +14048,11 @@
       <c r="AQ73" t="inlineStr"/>
       <c r="AR73" t="inlineStr">
         <is>
+          <t>PHYSIOTENS O.4 MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
           <t>SKU-CA539A2D2064</t>
         </is>
       </c>
@@ -13715,7 +14080,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -13868,6 +14233,11 @@
       <c r="AQ74" t="inlineStr"/>
       <c r="AR74" t="inlineStr">
         <is>
+          <t>PHYSIOTENS 0.2 MG F.C TAB</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
           <t>SKU-B7C323F6384A</t>
         </is>
       </c>
@@ -13895,7 +14265,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14054,6 +14424,11 @@
       </c>
       <c r="AR75" t="inlineStr">
         <is>
+          <t>NOSPASM 10 MG TAB</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
           <t>SKU-A8D02C4D1D50</t>
         </is>
       </c>
@@ -14081,7 +14456,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14238,6 +14613,11 @@
       </c>
       <c r="AR76" t="inlineStr">
         <is>
+          <t>MAALOX SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
           <t>SKU-CF8F6E331032</t>
         </is>
       </c>
@@ -14265,7 +14645,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14422,6 +14802,11 @@
       </c>
       <c r="AR77" t="inlineStr">
         <is>
+          <t>MAALOX PLUS SUSP.</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
           <t>SKU-1AF924FF9D0A</t>
         </is>
       </c>
@@ -14449,7 +14834,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14600,6 +14985,11 @@
       <c r="AQ78" t="inlineStr"/>
       <c r="AR78" t="inlineStr">
         <is>
+          <t>LYRICA 75 MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
           <t>SKU-AAE7A94D7393</t>
         </is>
       </c>
@@ -14627,7 +15017,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -14790,6 +15180,11 @@
       </c>
       <c r="AR79" t="inlineStr">
         <is>
+          <t>LYRICA 75</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
           <t>SKU-363F08F7C74B</t>
         </is>
       </c>
@@ -14817,7 +15212,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -14976,6 +15371,11 @@
       <c r="AQ80" t="inlineStr"/>
       <c r="AR80" t="inlineStr">
         <is>
+          <t>LYRICA 50</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
           <t>SKU-C0A6D001D8AF</t>
         </is>
       </c>
@@ -15003,7 +15403,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15162,6 +15562,11 @@
       <c r="AQ81" t="inlineStr"/>
       <c r="AR81" t="inlineStr">
         <is>
+          <t>LYRICA 300</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
           <t>SKU-F098A5FD5BEE</t>
         </is>
       </c>
@@ -15189,7 +15594,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15340,6 +15745,11 @@
       <c r="AQ82" t="inlineStr"/>
       <c r="AR82" t="inlineStr">
         <is>
+          <t>LYRICA 25</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
           <t>SKU-D44679BAC488</t>
         </is>
       </c>
@@ -15367,7 +15777,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15530,6 +15940,11 @@
       </c>
       <c r="AR83" t="inlineStr">
         <is>
+          <t>LYRICA 150</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
           <t>SKU-D45ECA3134D2</t>
         </is>
       </c>
@@ -15557,7 +15972,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15712,6 +16127,11 @@
       <c r="AQ84" t="inlineStr"/>
       <c r="AR84" t="inlineStr">
         <is>
+          <t>LUSTRAL 50MG TAB</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
           <t>SKU-6A963F4D9172</t>
         </is>
       </c>
@@ -15739,7 +16159,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -15888,6 +16308,11 @@
       <c r="AQ85" t="inlineStr"/>
       <c r="AR85" t="inlineStr">
         <is>
+          <t>MALARONE</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
           <t>SKU-8110ACD66DED</t>
         </is>
       </c>
@@ -15915,7 +16340,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16070,6 +16495,11 @@
       <c r="AQ86" t="inlineStr"/>
       <c r="AR86" t="inlineStr">
         <is>
+          <t>LUMIGAN 0.1MG/ML EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
           <t>SKU-F85B8E3B5AF5</t>
         </is>
       </c>
@@ -16097,7 +16527,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16248,6 +16678,11 @@
       </c>
       <c r="AR87" t="inlineStr">
         <is>
+          <t>MAGNACEF 200MG CAP.</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
           <t>SKU-FBF6E05266DB</t>
         </is>
       </c>
@@ -16275,7 +16710,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16434,6 +16869,11 @@
       </c>
       <c r="AR88" t="inlineStr">
         <is>
+          <t>MAGNACEF 100MG\5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
           <t>SKU-9C8A4E49AF5E</t>
         </is>
       </c>
@@ -16461,7 +16901,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16614,6 +17054,11 @@
       </c>
       <c r="AR89" t="inlineStr">
         <is>
+          <t>MADOPAR 250 MG TABS</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
           <t>SKU-3DED3EF6ADE4</t>
         </is>
       </c>
@@ -16641,7 +17086,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16800,6 +17245,11 @@
       </c>
       <c r="AR90" t="inlineStr">
         <is>
+          <t>MAGNACEF 400MG CAP</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
           <t>SKU-E0015787378D</t>
         </is>
       </c>
@@ -16827,7 +17277,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -16982,6 +17432,11 @@
       <c r="AQ91" t="inlineStr"/>
       <c r="AR91" t="inlineStr">
         <is>
+          <t>LORINEX 0.5MG-1ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
           <t>SKU-CF10C9B6E445</t>
         </is>
       </c>
@@ -17009,7 +17464,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17164,6 +17619,11 @@
       <c r="AQ92" t="inlineStr"/>
       <c r="AR92" t="inlineStr">
         <is>
+          <t>LORINE 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
           <t>SKU-18645274F607</t>
         </is>
       </c>
@@ -17191,7 +17651,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17346,6 +17806,11 @@
       <c r="AQ93" t="inlineStr"/>
       <c r="AR93" t="inlineStr">
         <is>
+          <t>LORINE 10MG TAB</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
           <t>SKU-A5BFD9741EA0</t>
         </is>
       </c>
@@ -17373,7 +17838,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17528,6 +17993,11 @@
       <c r="AQ94" t="inlineStr"/>
       <c r="AR94" t="inlineStr">
         <is>
+          <t>LORINE 10MG FAST MELTING TABLETS</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
           <t>SKU-42C16C10345D</t>
         </is>
       </c>
@@ -17555,7 +18025,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17716,6 +18186,11 @@
       <c r="AQ95" t="inlineStr"/>
       <c r="AR95" t="inlineStr">
         <is>
+          <t>LORINASE SYRUP</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
           <t>SKU-44033635AED3</t>
         </is>
       </c>
@@ -17743,7 +18218,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -17898,6 +18373,11 @@
       <c r="AQ96" t="inlineStr"/>
       <c r="AR96" t="inlineStr">
         <is>
+          <t>Purout 100 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
           <t>SKU-5A2C84ACC57F</t>
         </is>
       </c>
@@ -17925,7 +18405,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18076,6 +18556,11 @@
       <c r="AQ97" t="inlineStr"/>
       <c r="AR97" t="inlineStr">
         <is>
+          <t>LORANO 10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
           <t>SKU-301845A915B4</t>
         </is>
       </c>
@@ -18103,7 +18588,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18254,6 +18739,11 @@
       </c>
       <c r="AR98" t="inlineStr">
         <is>
+          <t>LORAMAX 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
           <t>SKU-C498CE94828D</t>
         </is>
       </c>
@@ -18281,7 +18771,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18436,6 +18926,11 @@
       <c r="AQ99" t="inlineStr"/>
       <c r="AR99" t="inlineStr">
         <is>
+          <t>LORAHIST 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
           <t>SKU-D1F83DB9887C</t>
         </is>
       </c>
@@ -18463,7 +18958,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18610,6 +19105,11 @@
       <c r="AQ100" t="inlineStr"/>
       <c r="AR100" t="inlineStr">
         <is>
+          <t>LORAHIST syrup</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
           <t>SKU-F269C3AC127A</t>
         </is>
       </c>
@@ -18637,7 +19137,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -18787,6 +19287,11 @@
       </c>
       <c r="AQ101" t="inlineStr"/>
       <c r="AR101" t="inlineStr">
+        <is>
+          <t>LORADAY 5 MG - 5 ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
         <is>
           <t>SKU-C44718F865AE</t>
         </is>
@@ -18803,7 +19308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18849,100 +19354,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -18974,7 +19484,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -18989,92 +19499,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-64124</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>319.53</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>230</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19106,7 +19621,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19121,92 +19636,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-13772</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>177.86</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>231</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19238,7 +19758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19253,92 +19773,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-14167</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>198.68</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>232</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19370,7 +19895,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19385,92 +19910,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-36728</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>180.29</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>233</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19502,7 +20032,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19517,92 +20047,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-82515</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>44.67</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>234</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19634,7 +20169,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -19649,92 +20184,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-93848</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>489.26</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>235</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19766,7 +20306,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -19781,92 +20321,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-88601</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>56.14</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>236</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19898,7 +20443,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -19913,92 +20458,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-40529</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>417.93</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>237</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20030,7 +20580,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20045,92 +20595,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-94050</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>190.5</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>238</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20162,7 +20717,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20177,92 +20732,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-35383</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>427.73</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>239</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20294,7 +20854,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20309,92 +20869,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-59197</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>63.12</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>240</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20426,7 +20991,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -20441,92 +21006,97 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>SKU-34313</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>34.64</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T13" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>241</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>100</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>12</v>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20543,7 +21113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20649,6 +21219,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -20684,7 +21264,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -20749,6 +21329,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-B1CDCF052505</t>
         </is>
@@ -20785,7 +21375,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -20850,6 +21440,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-433F5D34E054</t>
         </is>
@@ -20886,7 +21486,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -20951,6 +21551,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-1C7309B4B9E6</t>
         </is>
@@ -20987,7 +21597,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21052,6 +21662,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-48934891C4EA</t>
         </is>
@@ -21088,7 +21708,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21153,6 +21773,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-5FB4CE2F11ED</t>
         </is>
@@ -21189,7 +21819,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21254,6 +21884,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-20838AD4407F</t>
         </is>
@@ -21290,7 +21930,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21355,6 +21995,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-CE4F38677C21</t>
         </is>
@@ -21391,7 +22041,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21456,6 +22106,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-24FA4AA199C9</t>
         </is>
@@ -21492,7 +22152,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21557,6 +22217,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-2AE5EAEABF3F</t>
         </is>
@@ -21593,7 +22263,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21658,6 +22328,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-A99E8B25CF3A</t>
         </is>
@@ -21694,7 +22374,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21759,6 +22439,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-3F447EA58B99</t>
         </is>
@@ -21795,7 +22485,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -21860,6 +22550,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-08617EBE3121</t>
         </is>
@@ -21896,7 +22596,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -21961,6 +22661,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-FAEC82876922</t>
         </is>
@@ -21997,7 +22707,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22062,6 +22772,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-B7721B957483</t>
         </is>
@@ -22098,7 +22818,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22163,6 +22883,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-A5A0EA4C4115</t>
         </is>
@@ -22199,7 +22929,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22264,6 +22994,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-2E035603AB05</t>
         </is>
@@ -22300,7 +23040,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22365,6 +23105,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-AB092E9E8C4E</t>
         </is>
@@ -22401,7 +23151,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22466,6 +23216,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-B0FD2D369033</t>
         </is>
@@ -22502,7 +23262,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22567,6 +23327,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-52B13406226C</t>
         </is>
@@ -22603,7 +23373,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22668,6 +23438,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-60364A7C01E1</t>
         </is>

--- a/product_upload/packages/3/file.xlsx
+++ b/product_upload/packages/3/file.xlsx
@@ -680,8 +680,16 @@
           <t>7000000286-250-100000073665</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>QUINOX 250 MG F- C TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -863,8 +871,16 @@
           <t>7000000960-40-100000073664</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>RAZON 40 MG E.C TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1424,8 +1440,16 @@
           <t>7000000386-25-100000073665</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>RAPIDUS 25MG F.C. TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1607,8 +1631,16 @@
           <t>7000000323-4-200000002099</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>QUESTRAN POWDER detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -2168,8 +2200,16 @@
           <t>7000000960-40-966966966002</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PROTON 40MG E.C TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2347,8 +2387,16 @@
           <t>7000000960-20-966966966002</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PROTON 20MG E.C TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2904,8 +2952,16 @@
           <t>7000000423-75-100000073664</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PROTHIADEN TAB 75MG detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3087,8 +3143,16 @@
           <t>7000000423-25-100000073375</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PROTHIADEN 25MG CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -4213,8 +4277,16 @@
           <t>7000000176-0.25-100000073846</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>PULMICORT0.25MG-ML SINGLE DOSE PLASTIC U detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>TABUK PHARMACEUTICAL MANUFACTURING CO.</t>
@@ -4585,8 +4657,16 @@
           <t>7000001052-300-100000073375</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PREGADEX 300 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -5150,8 +5230,16 @@
           <t>14000001332-225-100000073863</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>PERGOVERIS 150/75 IU vial detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -6477,8 +6565,16 @@
           <t>7000000966-40-100000073664</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>PAXITAB 40MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -8160,8 +8256,16 @@
           <t>7000000817-1-100000073658</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>PENTASA 1GM PROLONGED RELEASE GRANULES detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8339,8 +8443,16 @@
           <t>7000000817-1-200000016459</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>PENTASA 1% ENEMA detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8892,8 +9004,16 @@
           <t>7000001331--200000016476</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>POLY-VI-SOL ORAL DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9075,8 +9195,16 @@
           <t>8000000140-1-100000073715</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>POLYTAR 1% LIQUID SHAMPOO detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9445,8 +9573,16 @@
           <t>7000001032-40-200000016467</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>POTASSIUM ACETATE INJ F.T.V. 40MEQ detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9628,8 +9764,16 @@
           <t>7000001033-7.5-100000073886</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>POTASSIUM CHLORIDE 7.5% AMP detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -9807,8 +9951,16 @@
           <t>7000001723-1-100000073652</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>PREDO 5MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10543,8 +10695,16 @@
           <t>7000001723-5-100000073664</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>PREDNISOLONE detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11303,8 +11463,16 @@
           <t>7000000340-110-100000073375</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>PRADAXA 110MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">ALPHA PHARMA INDUSTRY </t>
@@ -11689,8 +11857,16 @@
           <t>7000001033-7.5-100000073886</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>POTASSIUM CHLORIDE 7.5% AMP detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -11868,8 +12044,16 @@
           <t>7000001033-7.5-100000073886</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>POTASSIUM CHLORIDE 7.5% AMP detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12051,8 +12235,16 @@
           <t>7000000340-75-100000073375</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>PRADAXA 75MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">ALPHA PHARMA INDUSTRY </t>
@@ -12419,8 +12611,16 @@
           <t>7000000402-60-100000073664</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>PHAZYME TAB 60MG detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -12594,8 +12794,16 @@
           <t>7000000402-60-100000073664</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>PHAZYME TAB 60MG detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -12968,8 +13176,16 @@
           <t>7000000632-4-100000073712</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>PHILAQUIN FORTE 4% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13338,8 +13554,16 @@
           <t>21000002530-5.1-100000073712</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>PIGMANORM detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14464,8 +14688,16 @@
           <t>14000000840-85-100000073362</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>MAALOX SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -14653,8 +14885,16 @@
           <t>21000001989-90-100000073362</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>MAALOX PLUS SUSP. detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -14842,8 +15082,16 @@
           <t>7000001052-75-100000073375</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>LYRICA 75 MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15602,8 +15850,16 @@
           <t>7000001052-25-100000073375</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>LYRICA 25 detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16167,8 +16423,16 @@
           <t>14000004961-350-100000073665</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>MALARONE detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16535,8 +16799,16 @@
           <t>7000000235-200-200000016452</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>MAGNACEF 200MG CAP. detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -16909,8 +17181,16 @@
           <t>14000004818-250-100000073664</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>MADOPAR 250 MG TABS detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -18413,8 +18693,16 @@
           <t>7000000773-10-100000073664</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>LORANO 10MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -18596,8 +18884,16 @@
           <t>7000000773-10-100000073664</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>LORAMAX 10 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -18966,8 +19262,16 @@
           <t>7000000773-1-100000073652</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>LORAHIST syrup detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19145,8 +19449,16 @@
           <t>7000000773-1-100000073652</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>LORADAY 5 MG - 5 ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/3/file.xlsx
+++ b/product_upload/packages/3/file.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
@@ -19666,7 +19666,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21425,7 +21425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21506,40 +21506,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -21619,38 +21624,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>431.78</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-B1CDCF052505</t>
         </is>
@@ -21730,38 +21740,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>456.59</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-433F5D34E054</t>
         </is>
@@ -21841,38 +21856,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>322.45</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-1C7309B4B9E6</t>
         </is>
@@ -21952,38 +21972,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>318.87</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-48934891C4EA</t>
         </is>
@@ -22063,38 +22088,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>281.21</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-5FB4CE2F11ED</t>
         </is>
@@ -22174,38 +22204,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>414.1</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-20838AD4407F</t>
         </is>
@@ -22285,38 +22320,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>190.09</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-CE4F38677C21</t>
         </is>
@@ -22396,38 +22436,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>458.64</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-24FA4AA199C9</t>
         </is>
@@ -22507,38 +22552,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>406.95</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-2AE5EAEABF3F</t>
         </is>
@@ -22618,38 +22668,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>197.52</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-A99E8B25CF3A</t>
         </is>
@@ -22729,38 +22784,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>124.8</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-3F447EA58B99</t>
         </is>
@@ -22840,38 +22900,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>179.03</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-08617EBE3121</t>
         </is>
@@ -22951,38 +23016,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>43.25</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-FAEC82876922</t>
         </is>
@@ -23062,38 +23132,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>308.44</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-B7721B957483</t>
         </is>
@@ -23173,38 +23248,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>67.98999999999999</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-A5A0EA4C4115</t>
         </is>
@@ -23284,38 +23364,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>483.55</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-2E035603AB05</t>
         </is>
@@ -23395,38 +23480,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>342.78</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-AB092E9E8C4E</t>
         </is>
@@ -23506,38 +23596,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>263.18</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-B0FD2D369033</t>
         </is>
@@ -23617,38 +23712,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>103.05</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-52B13406226C</t>
         </is>
@@ -23728,38 +23828,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>432.78</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-60364A7C01E1</t>
         </is>
